--- a/캐시바이_SH_비전기로_등록본_1.xlsx
+++ b/캐시바이_SH_비전기로_등록본_1.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N351"/>
+  <dimension ref="A1:N421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -17615,13 +17615,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/muffle-1050/</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
       <c r="L308" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M308" t="inlineStr"/>
       <c r="N308" t="inlineStr">
         <is>
           <t>삼흥에너지 1050℃ 머플로(박스 전기로) 3L SH-FU-3MGE</t>
@@ -17671,13 +17669,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/muffle-1050/</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
       <c r="L309" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M309" t="inlineStr"/>
       <c r="N309" t="inlineStr">
         <is>
           <t>삼흥에너지 1050℃ 머플로(박스 전기로) 5L SH-FU-5MGE</t>
@@ -17727,13 +17723,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/muffle-1050/</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
       <c r="L310" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M310" t="inlineStr"/>
       <c r="N310" t="inlineStr">
         <is>
           <t>삼흥에너지 1050℃ 머플로(박스 전기로) 7L SH-FU-7MGE</t>
@@ -17783,13 +17777,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/muffle-1050/</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
       <c r="L311" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M311" t="inlineStr"/>
       <c r="N311" t="inlineStr">
         <is>
           <t>삼흥에너지 1050℃ 머플로(박스 전기로) 11L SH-FU-11MGE</t>
@@ -17839,13 +17831,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/muffle-1200/</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
       <c r="L312" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M312" t="inlineStr"/>
       <c r="N312" t="inlineStr">
         <is>
           <t>삼흥에너지 1200℃ 머플로(박스 전기로) 3L SH-FU-3MG</t>
@@ -17895,13 +17885,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/muffle-1200/</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
       <c r="L313" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M313" t="inlineStr"/>
       <c r="N313" t="inlineStr">
         <is>
           <t>삼흥에너지 1200℃ 머플로(박스 전기로) 5L SH-FU-5MG</t>
@@ -17951,13 +17939,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/muffle-1200/</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
       <c r="L314" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M314" t="inlineStr"/>
       <c r="N314" t="inlineStr">
         <is>
           <t>삼흥에너지 1200℃ 머플로(박스 전기로) 13L SH-FU-14MG</t>
@@ -18007,13 +17993,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/muffle-1200/</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
       <c r="L315" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M315" t="inlineStr"/>
       <c r="N315" t="inlineStr">
         <is>
           <t>삼흥에너지 1200℃ 머플로(박스 전기로) 27L SH-FU-27MG</t>
@@ -18063,13 +18047,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/muffle-1200/</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
       <c r="L316" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M316" t="inlineStr"/>
       <c r="N316" t="inlineStr">
         <is>
           <t>삼흥에너지 1200℃ 머플로(박스 전기로) 64L SH-FU-64MG</t>
@@ -18119,13 +18101,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/muffle-1200/</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
       <c r="L317" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M317" t="inlineStr"/>
       <c r="N317" t="inlineStr">
         <is>
           <t>삼흥에너지 1200℃ 머플로(박스 전기로) 125L SH-FU-125MG</t>
@@ -18175,13 +18155,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/muffle-1500/</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
       <c r="L318" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M318" t="inlineStr"/>
       <c r="N318" t="inlineStr">
         <is>
           <t>삼흥에너지 1500℃ 머플로(박스 전기로) 4.5L SH-FU-4MH</t>
@@ -18231,13 +18209,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/muffle-1500/</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
       <c r="L319" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M319" t="inlineStr"/>
       <c r="N319" t="inlineStr">
         <is>
           <t>삼흥에너지 1500℃ 머플로(박스 전기로) 10.8L SH-FU-11MH</t>
@@ -18287,13 +18263,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/muffle-1500/</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
       <c r="L320" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M320" t="inlineStr"/>
       <c r="N320" t="inlineStr">
         <is>
           <t>삼흥에너지 1500℃ 머플로(박스 전기로) 21.8L SH-FU-22MH</t>
@@ -18343,13 +18317,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/muffle-1500/</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
       <c r="L321" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M321" t="inlineStr"/>
       <c r="N321" t="inlineStr">
         <is>
           <t>삼흥에너지 1500℃ 머플로(박스 전기로) 36L SH-FU-36MH</t>
@@ -18399,13 +18371,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/vacuum-muffle-1200/</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
       <c r="L322" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M322" t="inlineStr"/>
       <c r="N322" t="inlineStr">
         <is>
           <t>삼흥에너지 1200℃ 진공 머플로 1.5L SH-FU-1.5MGV</t>
@@ -18455,13 +18425,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/vacuum-muffle-1200/</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
       <c r="L323" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M323" t="inlineStr"/>
       <c r="N323" t="inlineStr">
         <is>
           <t>삼흥에너지 1200℃ 진공 머플로 10L SH-FU-10MGV</t>
@@ -18511,13 +18479,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/vacuum-muffle-1200/</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
       <c r="L324" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M324" t="inlineStr"/>
       <c r="N324" t="inlineStr">
         <is>
           <t>삼흥에너지 1200℃ 진공 머플로 31L SH-FU-31MGV</t>
@@ -18567,13 +18533,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/vacuum-muffle-1200-quartz/</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
       <c r="L325" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M325" t="inlineStr"/>
       <c r="N325" t="inlineStr">
         <is>
           <t>삼흥에너지 1200℃ 진공 머플로 석영챔버형 1.5L SH-FU-1.5MGVQ</t>
@@ -18623,13 +18587,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/vacuum-muffle-1200-quartz/</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
       <c r="L326" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M326" t="inlineStr"/>
       <c r="N326" t="inlineStr">
         <is>
           <t>삼흥에너지 1200℃ 진공 머플로 석영챔버형 10L SH-FU-10MGVQ</t>
@@ -18679,13 +18641,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/vacuum-muffle-1200-quartz/</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
       <c r="L327" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M327" t="inlineStr"/>
       <c r="N327" t="inlineStr">
         <is>
           <t>삼흥에너지 1200℃ 진공 머플로 석영챔버형 31L SH-FU-31MGVQ</t>
@@ -18735,13 +18695,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/vacuum-muffle-1500/</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
       <c r="L328" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M328" t="inlineStr"/>
       <c r="N328" t="inlineStr">
         <is>
           <t>삼흥에너지 1500℃ 진공 머플로 4.5L SH-FU-4.5MHV</t>
@@ -18791,13 +18749,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/vacuum-muffle-1500/</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
       <c r="L329" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M329" t="inlineStr"/>
       <c r="N329" t="inlineStr">
         <is>
           <t>삼흥에너지 1500℃ 진공 머플로 18.7L SH-FU-18.7MHV</t>
@@ -18847,13 +18803,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/vacuum-muffle-1900/</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
       <c r="L330" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M330" t="inlineStr"/>
       <c r="N330" t="inlineStr">
         <is>
           <t>삼흥에너지 1900℃급 진공 머플로 4.5L SH-FU-4.5MSV</t>
@@ -18903,13 +18857,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/vacuum-muffle-1900/</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
       <c r="L331" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M331" t="inlineStr"/>
       <c r="N331" t="inlineStr">
         <is>
           <t>삼흥에너지 1900℃급 진공 머플로 10L SH-FU-10MSV</t>
@@ -18959,13 +18911,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/vacuum-muffle-1900/</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
       <c r="L332" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M332" t="inlineStr"/>
       <c r="N332" t="inlineStr">
         <is>
           <t>삼흥에너지 1900℃급 진공 머플로 18.7L SH-FU-18.7MSV</t>
@@ -19015,13 +18965,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/rotary-batch-300/</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
       <c r="L333" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M333" t="inlineStr"/>
       <c r="N333" t="inlineStr">
         <is>
           <t>삼흥에너지 1200℃ 배치식 회전튜브전기로 300mm 튜브 120Φ SH-FU-120RTG300</t>
@@ -19071,13 +19019,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/rotary-batch-300/</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
       <c r="L334" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M334" t="inlineStr"/>
       <c r="N334" t="inlineStr">
         <is>
           <t>삼흥에너지 1200℃ 배치식 회전튜브전기로 300mm 튜브 200Φ SH-FU-200RTG300</t>
@@ -19127,13 +19073,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/rotary-batch-300/</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
       <c r="L335" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M335" t="inlineStr"/>
       <c r="N335" t="inlineStr">
         <is>
           <t>삼흥에너지 1200℃ 배치식 회전튜브전기로 300mm 튜브 250Φ SH-FU-250RTG300</t>
@@ -19183,13 +19127,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/rotary-batch-3zone/</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
       <c r="L336" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M336" t="inlineStr"/>
       <c r="N336" t="inlineStr">
         <is>
           <t>삼흥에너지 1200℃ 배치식 회전튜브전기로 3zone 튜브 120Φ SH-FU-120RTG900</t>
@@ -19239,13 +19181,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/rotary-batch-3zone/</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
       <c r="L337" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M337" t="inlineStr"/>
       <c r="N337" t="inlineStr">
         <is>
           <t>삼흥에너지 1200℃ 배치식 회전튜브전기로 3zone 튜브 200Φ SH-FU-200RTG900</t>
@@ -19295,13 +19235,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/rotary-batch-3zone/</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
       <c r="L338" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M338" t="inlineStr"/>
       <c r="N338" t="inlineStr">
         <is>
           <t>삼흥에너지 1200℃ 배치식 회전튜브전기로 3zone 튜브 250Φ SH-FU-250RTG900</t>
@@ -19351,13 +19289,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/rotary-kiln-1200-2zone/</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
       <c r="L339" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M339" t="inlineStr"/>
       <c r="N339" t="inlineStr">
         <is>
           <t>삼흥에너지 1200℃ 연속식 회전튜브전기로(Rotary Kiln) 2 Zone 튜브 100Φ SH-FU-100RKG600</t>
@@ -19407,13 +19343,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/rotary-kiln-1200-2zone/</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
       <c r="L340" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M340" t="inlineStr"/>
       <c r="N340" t="inlineStr">
         <is>
           <t>삼흥에너지 1200℃ 연속식 회전튜브전기로(Rotary Kiln) 2 Zone 튜브 120Φ SH-FU-120RKG600</t>
@@ -19463,13 +19397,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/rotary-kiln-1200-2zone/</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
       <c r="L341" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M341" t="inlineStr"/>
       <c r="N341" t="inlineStr">
         <is>
           <t>삼흥에너지 1200℃ 연속식 회전튜브전기로(Rotary Kiln) 2 Zone 튜브 140Φ SH-FU-140RKG600</t>
@@ -19519,13 +19451,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/rotary-kiln-1200-3zone/</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
       <c r="L342" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M342" t="inlineStr"/>
       <c r="N342" t="inlineStr">
         <is>
           <t>삼흥에너지 1200℃ 연속식 회전튜브전기로(Rotary Kiln) 3 Zone 튜브 100Φ SH-FU-100RKG900</t>
@@ -19575,13 +19505,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/rotary-kiln-1200-3zone/</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
       <c r="L343" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M343" t="inlineStr"/>
       <c r="N343" t="inlineStr">
         <is>
           <t>삼흥에너지 1200℃ 연속식 회전튜브전기로(Rotary Kiln) 3 Zone 튜브 120Φ SH-FU-120RKG900</t>
@@ -19631,13 +19559,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/rotary-kiln-1200-3zone/</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
       <c r="L344" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M344" t="inlineStr"/>
       <c r="N344" t="inlineStr">
         <is>
           <t>삼흥에너지 1200℃ 연속식 회전튜브전기로(Rotary Kiln) 3 Zone 튜브 140Φ SH-FU-140RKG900</t>
@@ -19687,13 +19613,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/elevator-1200/</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
       <c r="L345" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M345" t="inlineStr"/>
       <c r="N345" t="inlineStr">
         <is>
           <t>삼흥에너지 1200℃ 엘레베이터로(자동 도어 승강) 3.5L SH-FU-3.5MGU</t>
@@ -19743,13 +19667,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/elevator-1200/</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
       <c r="L346" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M346" t="inlineStr"/>
       <c r="N346" t="inlineStr">
         <is>
           <t>삼흥에너지 1200℃ 엘레베이터로(자동 도어 승강) 6.4L SH-FU-6.5MGU</t>
@@ -19799,13 +19721,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/elevator-1500/</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
       <c r="L347" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M347" t="inlineStr"/>
       <c r="N347" t="inlineStr">
         <is>
           <t>삼흥에너지 1500℃ 엘레베이터로(자동 도어 승강) 2.2L SH-FU-2MHU</t>
@@ -19855,13 +19775,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/elevator-1500/</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
       <c r="L348" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M348" t="inlineStr"/>
       <c r="N348" t="inlineStr">
         <is>
           <t>삼흥에너지 1500℃ 엘레베이터로(자동 도어 승강) 3.8L SH-FU-4MHU</t>
@@ -19911,13 +19829,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/elevator-1500/</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
       <c r="L349" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M349" t="inlineStr"/>
       <c r="N349" t="inlineStr">
         <is>
           <t>삼흥에너지 1500℃ 엘레베이터로(자동 도어 승강) 6.2L SH-FU-6MHU</t>
@@ -19967,13 +19883,11 @@
           <t>https://rndsetup.com/brands/sh-scientific/steam-generator/</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
       <c r="L350" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M350" t="inlineStr"/>
       <c r="N350" t="inlineStr">
         <is>
           <t>삼흥에너지 스팀 제너레이터(Steam Generator) SH-SMARTSTEAM1</t>
@@ -20023,16 +19937,3820 @@
           <t>https://rndsetup.com/brands/sh-scientific/steam-generator/</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
       <c r="L351" t="inlineStr">
         <is>
           <t>재고 문의</t>
         </is>
       </c>
-      <c r="M351" t="inlineStr"/>
       <c r="N351" t="inlineStr">
         <is>
           <t>삼흥에너지 스팀 제너레이터(Steam Generator) SH-SMARTSTEAM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>349</v>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>SH-FU-4MS1700</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>삼흥에너지 MoSi₂ 머플 전기로 1700℃ 4.5L SH-FU-4MS1700</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F352" t="n">
+        <v>11400000</v>
+      </c>
+      <c r="G352" t="n">
+        <v>11640000</v>
+      </c>
+      <c r="H352" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/muffle-1700/</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>삼흥에너지 MoSi₂ 머플 전기로 1700℃ 4.5L SH-FU-4MS1700</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>350</v>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>SH-FU-11MS1700</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>삼흥에너지 MoSi₂ 머플 전기로 1700℃ 11L SH-FU-11MS1700</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F353" t="n">
+        <v>14155000</v>
+      </c>
+      <c r="G353" t="n">
+        <v>14453000</v>
+      </c>
+      <c r="H353" t="n">
+        <v>14900000</v>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/muffle-1700/</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>삼흥에너지 MoSi₂ 머플 전기로 1700℃ 11L SH-FU-11MS1700</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>351</v>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>SH-FU-22MS1700</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>삼흥에너지 MoSi₂ 머플 전기로 1700℃ 22L SH-FU-22MS1700</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F354" t="n">
+        <v>20615000</v>
+      </c>
+      <c r="G354" t="n">
+        <v>21049000</v>
+      </c>
+      <c r="H354" t="n">
+        <v>21700000</v>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/muffle-1700/</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>삼흥에너지 MoSi₂ 머플 전기로 1700℃ 22L SH-FU-22MS1700</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>352</v>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>SH-FU-4MS1800</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>삼흥에너지 MoSi₂ 머플 전기로 1800℃ 4.5L SH-FU-4MS1800</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F355" t="n">
+        <v>13556500</v>
+      </c>
+      <c r="G355" t="n">
+        <v>13841900</v>
+      </c>
+      <c r="H355" t="n">
+        <v>14270000</v>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/muffle-1800/</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>삼흥에너지 MoSi₂ 머플 전기로 1800℃ 4.5L SH-FU-4MS1800</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>353</v>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>SH-FU-11MS1800</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>삼흥에너지 MoSi₂ 머플 전기로 1800℃ 11L SH-FU-11MS1800</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F356" t="n">
+        <v>17432500</v>
+      </c>
+      <c r="G356" t="n">
+        <v>17799500</v>
+      </c>
+      <c r="H356" t="n">
+        <v>18350000</v>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/muffle-1800/</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>삼흥에너지 MoSi₂ 머플 전기로 1800℃ 11L SH-FU-11MS1800</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>354</v>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>SH-FU-22MS1800</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>삼흥에너지 MoSi₂ 머플 전기로 1800℃ 22L SH-FU-22MS1800</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F357" t="n">
+        <v>23303500</v>
+      </c>
+      <c r="G357" t="n">
+        <v>23794100</v>
+      </c>
+      <c r="H357" t="n">
+        <v>24530000</v>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/muffle-1800/</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>삼흥에너지 MoSi₂ 머플 전기로 1800℃ 22L SH-FU-22MS1800</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>355</v>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>SH-FU-4MS1900</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>삼흥에너지 MoSi₂ 머플 전기로 1900℃ 4.5L SH-FU-4MS1900</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F358" t="n">
+        <v>14820000</v>
+      </c>
+      <c r="G358" t="n">
+        <v>15132000</v>
+      </c>
+      <c r="H358" t="n">
+        <v>15600000</v>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/muffle-1900/</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>삼흥에너지 MoSi₂ 머플 전기로 1900℃ 4.5L SH-FU-4MS1900</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>356</v>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>SH-FU-11MS1900</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>삼흥에너지 MoSi₂ 머플 전기로 1900℃ 11L SH-FU-11MS1900</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F359" t="n">
+        <v>18810000</v>
+      </c>
+      <c r="G359" t="n">
+        <v>19206000</v>
+      </c>
+      <c r="H359" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/muffle-1900/</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>삼흥에너지 MoSi₂ 머플 전기로 1900℃ 11L SH-FU-11MS1900</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>357</v>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>SH-FU-22MS1900</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>삼흥에너지 MoSi₂ 머플 전기로 1900℃ 22L SH-FU-22MS1900</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F360" t="n">
+        <v>27265000</v>
+      </c>
+      <c r="G360" t="n">
+        <v>27839000</v>
+      </c>
+      <c r="H360" t="n">
+        <v>28700000</v>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/muffle-1900/</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>삼흥에너지 MoSi₂ 머플 전기로 1900℃ 22L SH-FU-22MS1900</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>358</v>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>SH-FU-2MSU-1800</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1800℃ 엘레베이터로 2.2L SH-FU-2MSU-1800</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F361" t="n">
+        <v>15447000</v>
+      </c>
+      <c r="G361" t="n">
+        <v>15772200</v>
+      </c>
+      <c r="H361" t="n">
+        <v>16260000</v>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/elevator-1800/</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1800℃ 엘레베이터로 2.2L SH-FU-2MSU-1800</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>359</v>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>SH-FU-4MSU-1800</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1800℃ 엘레베이터로 3.8L SH-FU-4MSU-1800</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F362" t="n">
+        <v>17318500</v>
+      </c>
+      <c r="G362" t="n">
+        <v>17683100</v>
+      </c>
+      <c r="H362" t="n">
+        <v>18230000</v>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/elevator-1800/</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1800℃ 엘레베이터로 3.8L SH-FU-4MSU-1800</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>360</v>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>SH-FU-6MSU-1800</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1800℃ 엘레베이터로 6.2L SH-FU-6MSU-1800</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F363" t="n">
+        <v>19076000</v>
+      </c>
+      <c r="G363" t="n">
+        <v>19477600</v>
+      </c>
+      <c r="H363" t="n">
+        <v>20080000</v>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/elevator-1800/</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1800℃ 엘레베이터로 6.2L SH-FU-6MSU-1800</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>361</v>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>SH-CVD-50TH300</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1500℃ 튜브로 가스플로 패키지 300mm Ø50 SH-CVD-50TH300</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F364" t="n">
+        <v>11181500</v>
+      </c>
+      <c r="G364" t="n">
+        <v>11416900</v>
+      </c>
+      <c r="H364" t="n">
+        <v>11770000</v>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/tube-1500/</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1500℃ 튜브로 가스플로 패키지 300mm Ø50 SH-CVD-50TH300</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>362</v>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>SH-CVD-80TH300</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1500℃ 튜브로 가스플로 패키지 300mm Ø80 SH-CVD-80TH300</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F365" t="n">
+        <v>12834500</v>
+      </c>
+      <c r="G365" t="n">
+        <v>13104700</v>
+      </c>
+      <c r="H365" t="n">
+        <v>13510000</v>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/tube-1500/</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1500℃ 튜브로 가스플로 패키지 300mm Ø80 SH-CVD-80TH300</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>363</v>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>SH-CVD-100TH300</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1500℃ 튜브로 가스플로 패키지 300mm Ø100 SH-CVD-100TH300</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F366" t="n">
+        <v>15846000</v>
+      </c>
+      <c r="G366" t="n">
+        <v>16179600</v>
+      </c>
+      <c r="H366" t="n">
+        <v>16680000</v>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/tube-1500/</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1500℃ 튜브로 가스플로 패키지 300mm Ø100 SH-CVD-100TH300</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>364</v>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>SH-CVD-120TH300</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1500℃ 튜브로 가스플로 패키지 300mm Ø120 SH-CVD-120TH300</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F367" t="n">
+        <v>18705500</v>
+      </c>
+      <c r="G367" t="n">
+        <v>19099300</v>
+      </c>
+      <c r="H367" t="n">
+        <v>19690000</v>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/tube-1500/</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1500℃ 튜브로 가스플로 패키지 300mm Ø120 SH-CVD-120TH300</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>365</v>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>SH-CVD-50TS300/18</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1800℃ 튜브로 가스플로 패키지 300mm Ø50 SH-CVD-50TS300/18</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F368" t="n">
+        <v>21717000</v>
+      </c>
+      <c r="G368" t="n">
+        <v>22174200</v>
+      </c>
+      <c r="H368" t="n">
+        <v>22860000</v>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/tube-1800/</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N368" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1800℃ 튜브로 가스플로 패키지 300mm Ø50 SH-CVD-50TS300/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>366</v>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>SH-CVD-80TS300/18</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1800℃ 튜브로 가스플로 패키지 300mm Ø80 SH-CVD-80TS300/18</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F369" t="n">
+        <v>24491000</v>
+      </c>
+      <c r="G369" t="n">
+        <v>25006600</v>
+      </c>
+      <c r="H369" t="n">
+        <v>25780000</v>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/tube-1800/</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1800℃ 튜브로 가스플로 패키지 300mm Ø80 SH-CVD-80TS300/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>367</v>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>SH-CVD-100TS300/18</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1800℃ 튜브로 가스플로 패키지 300mm Ø100 SH-CVD-100TS300/18</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F370" t="n">
+        <v>29241000</v>
+      </c>
+      <c r="G370" t="n">
+        <v>29856600</v>
+      </c>
+      <c r="H370" t="n">
+        <v>30780000</v>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/tube-1800/</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1800℃ 튜브로 가스플로 패키지 300mm Ø100 SH-CVD-100TS300/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>368</v>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>SH-CVD-120TS300/18</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1800℃ 튜브로 가스플로 패키지 300mm Ø120 SH-CVD-120TS300/18</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F371" t="n">
+        <v>32547000</v>
+      </c>
+      <c r="G371" t="n">
+        <v>33232200</v>
+      </c>
+      <c r="H371" t="n">
+        <v>34260000</v>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/tube-1800/</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N371" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1800℃ 튜브로 가스플로 패키지 300mm Ø120 SH-CVD-120TS300/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>369</v>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>SH-CVD-50TG300</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 튜브로 가스플로 패키지 300mm Ø50 SH-CVD-50TG300</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F372" t="n">
+        <v>5553700</v>
+      </c>
+      <c r="G372" t="n">
+        <v>5670620</v>
+      </c>
+      <c r="H372" t="n">
+        <v>5846000</v>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/gas-flow-package/</t>
+        </is>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N372" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 튜브로 가스플로 패키지 300mm Ø50 SH-CVD-50TG300</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>370</v>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>SH-CVD-80TG300</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 튜브로 가스플로 패키지 300mm Ø80 SH-CVD-80TG300</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F373" t="n">
+        <v>6897000</v>
+      </c>
+      <c r="G373" t="n">
+        <v>7042200</v>
+      </c>
+      <c r="H373" t="n">
+        <v>7260000</v>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/gas-flow-package/</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N373" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 튜브로 가스플로 패키지 300mm Ø80 SH-CVD-80TG300</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>371</v>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>SH-CVD-100TG300</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 튜브로 가스플로 패키지 300mm Ø100 SH-CVD-100TG300</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F374" t="n">
+        <v>8417000</v>
+      </c>
+      <c r="G374" t="n">
+        <v>8594200</v>
+      </c>
+      <c r="H374" t="n">
+        <v>8860000</v>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/gas-flow-package/</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N374" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 튜브로 가스플로 패키지 300mm Ø100 SH-CVD-100TG300</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>372</v>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>SH-CVD-120TG300</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 튜브로 가스플로 패키지 300mm Ø120 SH-CVD-120TG300</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F375" t="n">
+        <v>10488000</v>
+      </c>
+      <c r="G375" t="n">
+        <v>10708800</v>
+      </c>
+      <c r="H375" t="n">
+        <v>11040000</v>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/gas-flow-package/</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N375" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 튜브로 가스플로 패키지 300mm Ø120 SH-CVD-120TG300</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>373</v>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>SH-CVD-200TG300</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 튜브로 가스플로 패키지 300mm Ø200 SH-CVD-200TG300</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F376" t="n">
+        <v>17318500</v>
+      </c>
+      <c r="G376" t="n">
+        <v>17683100</v>
+      </c>
+      <c r="H376" t="n">
+        <v>18230000</v>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/gas-flow-package/</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N376" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 튜브로 가스플로 패키지 300mm Ø200 SH-CVD-200TG300</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>374</v>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>SH-CVD-250TG300</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 튜브로 가스플로 패키지 300mm Ø250 SH-CVD-250TG300</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F377" t="n">
+        <v>21821500</v>
+      </c>
+      <c r="G377" t="n">
+        <v>22280900</v>
+      </c>
+      <c r="H377" t="n">
+        <v>22970000</v>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/gas-flow-package/</t>
+        </is>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N377" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 튜브로 가스플로 패키지 300mm Ø250 SH-CVD-250TG300</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>375</v>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>SH-CVD-50TG600</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 튜브로 가스플로 패키지 600mm Ø50 SH-CVD-50TG600</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F378" t="n">
+        <v>6949250</v>
+      </c>
+      <c r="G378" t="n">
+        <v>7095550</v>
+      </c>
+      <c r="H378" t="n">
+        <v>7315000</v>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/gas-flow-package-600mm/</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N378" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 튜브로 가스플로 패키지 600mm Ø50 SH-CVD-50TG600</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>376</v>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>SH-CVD-80TG600</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 튜브로 가스플로 패키지 600mm Ø80 SH-CVD-80TG600</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F379" t="n">
+        <v>8578500</v>
+      </c>
+      <c r="G379" t="n">
+        <v>8759100</v>
+      </c>
+      <c r="H379" t="n">
+        <v>9030000</v>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/gas-flow-package-600mm/</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N379" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 튜브로 가스플로 패키지 600mm Ø80 SH-CVD-80TG600</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>377</v>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>SH-CVD-100TG600</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 튜브로 가스플로 패키지 600mm Ø100 SH-CVD-100TG600</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F380" t="n">
+        <v>10307500</v>
+      </c>
+      <c r="G380" t="n">
+        <v>10524500</v>
+      </c>
+      <c r="H380" t="n">
+        <v>10850000</v>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/gas-flow-package-600mm/</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N380" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 튜브로 가스플로 패키지 600mm Ø100 SH-CVD-100TG600</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>378</v>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>SH-CVD-120TG600</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 튜브로 가스플로 패키지 600mm Ø120 SH-CVD-120TG600</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F381" t="n">
+        <v>11856000</v>
+      </c>
+      <c r="G381" t="n">
+        <v>12105600</v>
+      </c>
+      <c r="H381" t="n">
+        <v>12480000</v>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/gas-flow-package-600mm/</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N381" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 튜브로 가스플로 패키지 600mm Ø120 SH-CVD-120TG600</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>379</v>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>SH-CVD-200TG600</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 튜브로 가스플로 패키지 600mm Ø200 SH-CVD-200TG600</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F382" t="n">
+        <v>23655000</v>
+      </c>
+      <c r="G382" t="n">
+        <v>24153000</v>
+      </c>
+      <c r="H382" t="n">
+        <v>24900000</v>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/gas-flow-package-600mm/</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N382" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 튜브로 가스플로 패키지 600mm Ø200 SH-CVD-200TG600</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>380</v>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>SH-CVD-250TG600</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 튜브로 가스플로 패키지 600mm Ø250 SH-CVD-250TG600</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F383" t="n">
+        <v>29944000</v>
+      </c>
+      <c r="G383" t="n">
+        <v>30574400</v>
+      </c>
+      <c r="H383" t="n">
+        <v>31520000</v>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/gas-flow-package-600mm/</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N383" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 튜브로 가스플로 패키지 600mm Ø250 SH-CVD-250TG600</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>381</v>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>SH-CVD-50TG200</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 3존 튜브로 가스플로 패키지 200mm×3 Ø50 SH-CVD-50TG200</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F384" t="n">
+        <v>9143750</v>
+      </c>
+      <c r="G384" t="n">
+        <v>9336250</v>
+      </c>
+      <c r="H384" t="n">
+        <v>9625000</v>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/gas-flow-3zone/</t>
+        </is>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N384" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 3존 튜브로 가스플로 패키지 200mm×3 Ø50 SH-CVD-50TG200</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>382</v>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>SH-CVD-80TG200</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 3존 튜브로 가스플로 패키지 200mm×3 Ø80 SH-CVD-80TG200</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F385" t="n">
+        <v>10735000</v>
+      </c>
+      <c r="G385" t="n">
+        <v>10961000</v>
+      </c>
+      <c r="H385" t="n">
+        <v>11300000</v>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/gas-flow-3zone/</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N385" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 3존 튜브로 가스플로 패키지 200mm×3 Ø80 SH-CVD-80TG200</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>383</v>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>SH-CVD-100TG200</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 3존 튜브로 가스플로 패키지 200mm×3 Ø100 SH-CVD-100TG200</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F386" t="n">
+        <v>12483000</v>
+      </c>
+      <c r="G386" t="n">
+        <v>12745800</v>
+      </c>
+      <c r="H386" t="n">
+        <v>13140000</v>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/gas-flow-3zone/</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N386" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 3존 튜브로 가스플로 패키지 200mm×3 Ø100 SH-CVD-100TG200</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>384</v>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>SH-CVD-120TG200</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 3존 튜브로 가스플로 패키지 200mm×3 Ø120 SH-CVD-120TG200</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F387" t="n">
+        <v>14126500</v>
+      </c>
+      <c r="G387" t="n">
+        <v>14423900</v>
+      </c>
+      <c r="H387" t="n">
+        <v>14870000</v>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/gas-flow-3zone/</t>
+        </is>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N387" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 3존 튜브로 가스플로 패키지 200mm×3 Ø120 SH-CVD-120TG200</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="n">
+        <v>385</v>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>SH-CVD-200TG200</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 3존 튜브로 가스플로 패키지 200mm×3 Ø200 SH-CVD-200TG200</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F388" t="n">
+        <v>25840000</v>
+      </c>
+      <c r="G388" t="n">
+        <v>26384000</v>
+      </c>
+      <c r="H388" t="n">
+        <v>27200000</v>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/gas-flow-3zone/</t>
+        </is>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N388" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 3존 튜브로 가스플로 패키지 200mm×3 Ø200 SH-CVD-200TG200</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="n">
+        <v>386</v>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>SH-CVD-250TG200</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 3존 튜브로 가스플로 패키지 200mm×3 Ø250 SH-CVD-250TG200</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F389" t="n">
+        <v>32794000</v>
+      </c>
+      <c r="G389" t="n">
+        <v>33484400</v>
+      </c>
+      <c r="H389" t="n">
+        <v>34520000</v>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/gas-flow-3zone/</t>
+        </is>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N389" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 3존 튜브로 가스플로 패키지 200mm×3 Ø250 SH-CVD-250TG200</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="n">
+        <v>387</v>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>SH-FU-120RTG300-1Z</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 회전튜브전기로 1존 300mm 튜브 120Φ SH-FU-120RTG300-1Z</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F390" t="n">
+        <v>12587500</v>
+      </c>
+      <c r="G390" t="n">
+        <v>12852500</v>
+      </c>
+      <c r="H390" t="n">
+        <v>13250000</v>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/rotary-tube-furnace/</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 회전튜브전기로 1존 300mm 튜브 120Φ SH-FU-120RTG300-1Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="n">
+        <v>388</v>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>SH-FU-200RTG300-1Z</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 회전튜브전기로 1존 300mm 튜브 200Φ SH-FU-200RTG300-1Z</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F391" t="n">
+        <v>18762500</v>
+      </c>
+      <c r="G391" t="n">
+        <v>19157500</v>
+      </c>
+      <c r="H391" t="n">
+        <v>19750000</v>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/rotary-tube-furnace/</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 회전튜브전기로 1존 300mm 튜브 200Φ SH-FU-200RTG300-1Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>389</v>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>SH-FU-250RTG300-1Z</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 회전튜브전기로 1존 300mm 튜브 250Φ SH-FU-250RTG300-1Z</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F392" t="n">
+        <v>22942500</v>
+      </c>
+      <c r="G392" t="n">
+        <v>23425500</v>
+      </c>
+      <c r="H392" t="n">
+        <v>24150000</v>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/rotary-tube-furnace/</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 회전튜브전기로 1존 300mm 튜브 250Φ SH-FU-250RTG300-1Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>390</v>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>SH-CVD-50TG300-PK</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 300mm Ø50 SH-CVD-50TG300-PK</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F393" t="n">
+        <v>9738450</v>
+      </c>
+      <c r="G393" t="n">
+        <v>9943470</v>
+      </c>
+      <c r="H393" t="n">
+        <v>10251000</v>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/vacuum-tube-turnkey/</t>
+        </is>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 300mm Ø50 SH-CVD-50TG300-PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>391</v>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>SH-CVD-80TG300-PK</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 300mm Ø80 SH-CVD-80TG300-PK</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F394" t="n">
+        <v>11081750</v>
+      </c>
+      <c r="G394" t="n">
+        <v>11315050</v>
+      </c>
+      <c r="H394" t="n">
+        <v>11665000</v>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/vacuum-tube-turnkey/</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 300mm Ø80 SH-CVD-80TG300-PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>392</v>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>SH-CVD-100TG300-PK</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 300mm Ø100 SH-CVD-100TG300-PK</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F395" t="n">
+        <v>12668250</v>
+      </c>
+      <c r="G395" t="n">
+        <v>12934950</v>
+      </c>
+      <c r="H395" t="n">
+        <v>13335000</v>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/vacuum-tube-turnkey/</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 300mm Ø100 SH-CVD-100TG300-PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>393</v>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>SH-CVD-120TG300-PK</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 300mm Ø120 SH-CVD-120TG300-PK</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F396" t="n">
+        <v>14739250</v>
+      </c>
+      <c r="G396" t="n">
+        <v>15049550</v>
+      </c>
+      <c r="H396" t="n">
+        <v>15515000</v>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/vacuum-tube-turnkey/</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 300mm Ø120 SH-CVD-120TG300-PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>394</v>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>SH-CVD-50TG600-PK</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 600mm Ø50 SH-CVD-50TG600-PK</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F397" t="n">
+        <v>11134000</v>
+      </c>
+      <c r="G397" t="n">
+        <v>11368400</v>
+      </c>
+      <c r="H397" t="n">
+        <v>11720000</v>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/vacuum-tube-turnkey/</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 600mm Ø50 SH-CVD-50TG600-PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>395</v>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>SH-CVD-80TG600-PK</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 600mm Ø80 SH-CVD-80TG600-PK</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F398" t="n">
+        <v>12763250</v>
+      </c>
+      <c r="G398" t="n">
+        <v>13031950</v>
+      </c>
+      <c r="H398" t="n">
+        <v>13435000</v>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/vacuum-tube-turnkey/</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 600mm Ø80 SH-CVD-80TG600-PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>396</v>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>SH-CVD-100TG600-PK</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 600mm Ø100 SH-CVD-100TG600-PK</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F399" t="n">
+        <v>14558750</v>
+      </c>
+      <c r="G399" t="n">
+        <v>14865250</v>
+      </c>
+      <c r="H399" t="n">
+        <v>15325000</v>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/vacuum-tube-turnkey/</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N399" t="inlineStr">
+        <is>
+          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 600mm Ø100 SH-CVD-100TG600-PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>397</v>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>SH-CVD-120TG600-PK</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 600mm Ø120 SH-CVD-120TG600-PK</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F400" t="n">
+        <v>16107250</v>
+      </c>
+      <c r="G400" t="n">
+        <v>16446350</v>
+      </c>
+      <c r="H400" t="n">
+        <v>16955000</v>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/vacuum-tube-turnkey/</t>
+        </is>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N400" t="inlineStr">
+        <is>
+          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 600mm Ø120 SH-CVD-120TG600-PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>398</v>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>SH-CVD-50TH300-PK</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>삼흥에너지 CVD 턴키 튜브로 1500℃ 300mm Ø50 SH-CVD-50TH300-PK</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F401" t="n">
+        <v>15366250</v>
+      </c>
+      <c r="G401" t="n">
+        <v>15689750</v>
+      </c>
+      <c r="H401" t="n">
+        <v>16175000</v>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/vacuum-tube-turnkey/</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N401" t="inlineStr">
+        <is>
+          <t>삼흥에너지 CVD 턴키 튜브로 1500℃ 300mm Ø50 SH-CVD-50TH300-PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="n">
+        <v>399</v>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>SH-CVD-80TH300-PK</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>삼흥에너지 CVD 턴키 튜브로 1500℃ 300mm Ø80 SH-CVD-80TH300-PK</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F402" t="n">
+        <v>17019250</v>
+      </c>
+      <c r="G402" t="n">
+        <v>17377550</v>
+      </c>
+      <c r="H402" t="n">
+        <v>17915000</v>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/vacuum-tube-turnkey/</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N402" t="inlineStr">
+        <is>
+          <t>삼흥에너지 CVD 턴키 튜브로 1500℃ 300mm Ø80 SH-CVD-80TH300-PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="n">
+        <v>400</v>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>SH-CVD-100TH300-PK</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>삼흥에너지 CVD 턴키 튜브로 1500℃ 300mm Ø100 SH-CVD-100TH300-PK</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F403" t="n">
+        <v>21009250</v>
+      </c>
+      <c r="G403" t="n">
+        <v>21451550</v>
+      </c>
+      <c r="H403" t="n">
+        <v>22115000</v>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/vacuum-tube-turnkey/</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N403" t="inlineStr">
+        <is>
+          <t>삼흥에너지 CVD 턴키 튜브로 1500℃ 300mm Ø100 SH-CVD-100TH300-PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="n">
+        <v>401</v>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>SH-CVD-120TH300-PK</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>삼흥에너지 CVD 턴키 튜브로 1500℃ 300mm Ø120 SH-CVD-120TH300-PK</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F404" t="n">
+        <v>23868750</v>
+      </c>
+      <c r="G404" t="n">
+        <v>24371250</v>
+      </c>
+      <c r="H404" t="n">
+        <v>25125000</v>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/vacuum-tube-turnkey/</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N404" t="inlineStr">
+        <is>
+          <t>삼흥에너지 CVD 턴키 튜브로 1500℃ 300mm Ø120 SH-CVD-120TH300-PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="n">
+        <v>402</v>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>SH-CVD-50TS300/18-PK</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>삼흥에너지 CVD 턴키 튜브로 1800℃ 300mm Ø50 SH-CVD-50TS300/18-PK</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F405" t="n">
+        <v>26908750</v>
+      </c>
+      <c r="G405" t="n">
+        <v>27475250</v>
+      </c>
+      <c r="H405" t="n">
+        <v>28325000</v>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/vacuum-tube-turnkey/</t>
+        </is>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N405" t="inlineStr">
+        <is>
+          <t>삼흥에너지 CVD 턴키 튜브로 1800℃ 300mm Ø50 SH-CVD-50TS300/18-PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="n">
+        <v>403</v>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>SH-CVD-80TS300/18-PK</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>삼흥에너지 CVD 턴키 튜브로 1800℃ 300mm Ø80 SH-CVD-80TS300/18-PK</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F406" t="n">
+        <v>29682750</v>
+      </c>
+      <c r="G406" t="n">
+        <v>30307650</v>
+      </c>
+      <c r="H406" t="n">
+        <v>31245000</v>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/vacuum-tube-turnkey/</t>
+        </is>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>삼흥에너지 CVD 턴키 튜브로 1800℃ 300mm Ø80 SH-CVD-80TS300/18-PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="n">
+        <v>404</v>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>SH-CVD-100TS300/18-PK</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>삼흥에너지 CVD 턴키 튜브로 1800℃ 300mm Ø100 SH-CVD-100TS300/18-PK</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F407" t="n">
+        <v>35658250</v>
+      </c>
+      <c r="G407" t="n">
+        <v>36408950</v>
+      </c>
+      <c r="H407" t="n">
+        <v>37535000</v>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/vacuum-tube-turnkey/</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N407" t="inlineStr">
+        <is>
+          <t>삼흥에너지 CVD 턴키 튜브로 1800℃ 300mm Ø100 SH-CVD-100TS300/18-PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="n">
+        <v>405</v>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>SH-CVD-120TS300/18-PK</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>삼흥에너지 CVD 턴키 튜브로 1800℃ 300mm Ø120 SH-CVD-120TS300/18-PK</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F408" t="n">
+        <v>38964250</v>
+      </c>
+      <c r="G408" t="n">
+        <v>39784550</v>
+      </c>
+      <c r="H408" t="n">
+        <v>41015000</v>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/vacuum-tube-turnkey/</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>삼흥에너지 CVD 턴키 튜브로 1800℃ 300mm Ø120 SH-CVD-120TS300/18-PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="n">
+        <v>406</v>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>SH-FU-2MSU-1700</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1700℃ 엘레베이터로 2.2L SH-FU-2MSU-1700</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F409" t="n">
+        <v>14250000</v>
+      </c>
+      <c r="G409" t="n">
+        <v>14550000</v>
+      </c>
+      <c r="H409" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/elevator-1700/</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr"/>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr"/>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1700℃ 엘레베이터로 2.2L SH-FU-2MSU-1700</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="n">
+        <v>407</v>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>SH-FU-4MSU-1700</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1700℃ 엘레베이터로 3.8L SH-FU-4MSU-1700</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F410" t="n">
+        <v>15722500</v>
+      </c>
+      <c r="G410" t="n">
+        <v>16053500</v>
+      </c>
+      <c r="H410" t="n">
+        <v>16550000</v>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/elevator-1700/</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr"/>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="M410" t="inlineStr"/>
+      <c r="N410" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1700℃ 엘레베이터로 3.8L SH-FU-4MSU-1700</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="n">
+        <v>408</v>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>SH-FU-6MSU-1700</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1700℃ 엘레베이터로 6.2L SH-FU-6MSU-1700</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F411" t="n">
+        <v>17480000</v>
+      </c>
+      <c r="G411" t="n">
+        <v>17848000</v>
+      </c>
+      <c r="H411" t="n">
+        <v>18400000</v>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/elevator-1700/</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr"/>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr"/>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1700℃ 엘레베이터로 6.2L SH-FU-6MSU-1700</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="n">
+        <v>409</v>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>SH-FU-100RKH600</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1500℃ 연속식 회전튜브전기로 2존 Φ100 SH-FU-100RKH600</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F412" t="n">
+        <v>47500000</v>
+      </c>
+      <c r="G412" t="n">
+        <v>48500000</v>
+      </c>
+      <c r="H412" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/rotary-kiln-1500-2zone/</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr"/>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr"/>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1500℃ 연속식 회전튜브전기로 2존 Φ100 SH-FU-100RKH600</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="n">
+        <v>410</v>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>SH-FU-120RKH600</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1500℃ 연속식 회전튜브전기로 2존 Φ120 SH-FU-120RKH600</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F413" t="n">
+        <v>55005000</v>
+      </c>
+      <c r="G413" t="n">
+        <v>56163000</v>
+      </c>
+      <c r="H413" t="n">
+        <v>57900000</v>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/rotary-kiln-1500-2zone/</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr"/>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr"/>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1500℃ 연속식 회전튜브전기로 2존 Φ120 SH-FU-120RKH600</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="n">
+        <v>411</v>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>SH-FU-100RKH900</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1500℃ 연속식 회전튜브전기로 3존 Φ100 SH-FU-100RKH900</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F414" t="n">
+        <v>57950000</v>
+      </c>
+      <c r="G414" t="n">
+        <v>59170000</v>
+      </c>
+      <c r="H414" t="n">
+        <v>61000000</v>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/rotary-kiln-1500-3zone/</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr"/>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr"/>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1500℃ 연속식 회전튜브전기로 3존 Φ100 SH-FU-100RKH900</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="n">
+        <v>412</v>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>SH-FU-120RKH900</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1500℃ 연속식 회전튜브전기로 3존 Φ120 SH-FU-120RKH900</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F415" t="n">
+        <v>67450000</v>
+      </c>
+      <c r="G415" t="n">
+        <v>68870000</v>
+      </c>
+      <c r="H415" t="n">
+        <v>71000000</v>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/rotary-kiln-1500-3zone/</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr"/>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr"/>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1500℃ 연속식 회전튜브전기로 3존 Φ120 SH-FU-120RKH900</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="n">
+        <v>413</v>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>SH-FU-5MGQ</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 석영챔버 머플로 4.5L SH-FU-5MGQ</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F416" t="n">
+        <v>3325000</v>
+      </c>
+      <c r="G416" t="n">
+        <v>3395000</v>
+      </c>
+      <c r="H416" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/muffle-1200-quartz/</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr"/>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr"/>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 석영챔버 머플로 4.5L SH-FU-5MGQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="n">
+        <v>414</v>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>SH-FU-14MGQ</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 석영챔버 머플로 14L SH-FU-14MGQ</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F417" t="n">
+        <v>4750000</v>
+      </c>
+      <c r="G417" t="n">
+        <v>4850000</v>
+      </c>
+      <c r="H417" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/muffle-1200-quartz/</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr"/>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr"/>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 석영챔버 머플로 14L SH-FU-14MGQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="n">
+        <v>415</v>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>SH-FU-27MGQ</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 석영챔버 머플로 27L SH-FU-27MGQ</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F418" t="n">
+        <v>7600000</v>
+      </c>
+      <c r="G418" t="n">
+        <v>7760000</v>
+      </c>
+      <c r="H418" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/muffle-1200-quartz/</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr"/>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr"/>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 석영챔버 머플로 27L SH-FU-27MGQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="n">
+        <v>416</v>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>SH-FU-64MGV</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 진공 머플로 64L SH-FU-64MGV</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F419" t="n">
+        <v>29877500</v>
+      </c>
+      <c r="G419" t="n">
+        <v>30506500</v>
+      </c>
+      <c r="H419" t="n">
+        <v>31450000</v>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/vacuum-muffle-1200/</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr"/>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr"/>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 진공 머플로 64L SH-FU-64MGV</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="n">
+        <v>417</v>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>SH-FU-125MGV</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 진공 머플로 125L SH-FU-125MGV</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F420" t="n">
+        <v>39653000</v>
+      </c>
+      <c r="G420" t="n">
+        <v>40487800</v>
+      </c>
+      <c r="H420" t="n">
+        <v>41740000</v>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/vacuum-muffle-1200/</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr"/>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr"/>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>삼흥에너지 1200℃ 진공 머플로 125L SH-FU-125MGV</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="n">
+        <v>418</v>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>SH Scientific</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>SH-LABSTEAM5</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>삼흥에너지 Benchtop 스팀 제너레이터 5L SH-LABSTEAM5</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="F421" t="n">
+        <v>2109000</v>
+      </c>
+      <c r="G421" t="n">
+        <v>2153400</v>
+      </c>
+      <c r="H421" t="n">
+        <v>2220000</v>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>https://rndsetup.com/brands/sh-scientific/steam-generator/</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr"/>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>재고 문의</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr"/>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>삼흥에너지 Benchtop 스팀 제너레이터 5L SH-LABSTEAM5</t>
         </is>
       </c>
     </row>

--- a/캐시바이_SH_비전기로_등록본_1.xlsx
+++ b/캐시바이_SH_비전기로_등록본_1.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N417"/>
+  <dimension ref="A1:N414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -20168,13 +20168,13 @@
         </is>
       </c>
       <c r="F331" t="n">
-        <v>13846250</v>
+        <v>12587500</v>
       </c>
       <c r="G331" t="n">
-        <v>14137750</v>
+        <v>12852500</v>
       </c>
       <c r="H331" t="n">
-        <v>14575000</v>
+        <v>13250000</v>
       </c>
       <c r="I331" t="inlineStr">
         <is>
@@ -20227,13 +20227,13 @@
         </is>
       </c>
       <c r="F332" t="n">
-        <v>20638750</v>
+        <v>18762500</v>
       </c>
       <c r="G332" t="n">
-        <v>21073250</v>
+        <v>19157500</v>
       </c>
       <c r="H332" t="n">
-        <v>21725000</v>
+        <v>19750000</v>
       </c>
       <c r="I332" t="inlineStr">
         <is>
@@ -20286,13 +20286,13 @@
         </is>
       </c>
       <c r="F333" t="n">
-        <v>25236750</v>
+        <v>22942500</v>
       </c>
       <c r="G333" t="n">
-        <v>25768050</v>
+        <v>23425500</v>
       </c>
       <c r="H333" t="n">
-        <v>26565000</v>
+        <v>24150000</v>
       </c>
       <c r="I333" t="inlineStr">
         <is>
@@ -20345,13 +20345,13 @@
         </is>
       </c>
       <c r="F334" t="n">
-        <v>27692500</v>
+        <v>25175000</v>
       </c>
       <c r="G334" t="n">
-        <v>28275500</v>
+        <v>25705000</v>
       </c>
       <c r="H334" t="n">
-        <v>29150000</v>
+        <v>26500000</v>
       </c>
       <c r="I334" t="inlineStr">
         <is>
@@ -20404,13 +20404,13 @@
         </is>
       </c>
       <c r="F335" t="n">
-        <v>40023500</v>
+        <v>36385000</v>
       </c>
       <c r="G335" t="n">
-        <v>40866100</v>
+        <v>37151000</v>
       </c>
       <c r="H335" t="n">
-        <v>42130000</v>
+        <v>38300000</v>
       </c>
       <c r="I335" t="inlineStr">
         <is>
@@ -20463,13 +20463,13 @@
         </is>
       </c>
       <c r="F336" t="n">
-        <v>50055500</v>
+        <v>45505000</v>
       </c>
       <c r="G336" t="n">
-        <v>51109300</v>
+        <v>46463000</v>
       </c>
       <c r="H336" t="n">
-        <v>52690000</v>
+        <v>47900000</v>
       </c>
       <c r="I336" t="inlineStr">
         <is>
@@ -21688,12 +21688,12 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>SH-FU-2MSU-1800</t>
+          <t>SH-FU-2MSU</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>삼흥에너지 1800℃ 엘레베이터로 2.2L SH-FU-2MSU-1800</t>
+          <t>삼흥에너지 1800℃ 엘레베이터로 2.2L SH-FU-2MSU</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -21732,7 +21732,7 @@
       </c>
       <c r="N357" t="inlineStr">
         <is>
-          <t>삼흥에너지 1800℃ 엘레베이터로 2.2L SH-FU-2MSU-1800</t>
+          <t>삼흥에너지 1800℃ 엘레베이터로 2.2L SH-FU-2MSU</t>
         </is>
       </c>
     </row>
@@ -21747,12 +21747,12 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>SH-FU-4MSU-1800</t>
+          <t>SH-FU-4MSU</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>삼흥에너지 1800℃ 엘레베이터로 3.8L SH-FU-4MSU-1800</t>
+          <t>삼흥에너지 1800℃ 엘레베이터로 3.8L SH-FU-4MSU</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -21791,7 +21791,7 @@
       </c>
       <c r="N358" t="inlineStr">
         <is>
-          <t>삼흥에너지 1800℃ 엘레베이터로 3.8L SH-FU-4MSU-1800</t>
+          <t>삼흥에너지 1800℃ 엘레베이터로 3.8L SH-FU-4MSU</t>
         </is>
       </c>
     </row>
@@ -21806,12 +21806,12 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>SH-FU-6MSU-1800</t>
+          <t>SH-FU-6MSU</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>삼흥에너지 1800℃ 엘레베이터로 6.2L SH-FU-6MSU-1800</t>
+          <t>삼흥에너지 1800℃ 엘레베이터로 6.2L SH-FU-6MSU</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -21850,7 +21850,7 @@
       </c>
       <c r="N359" t="inlineStr">
         <is>
-          <t>삼흥에너지 1800℃ 엘레베이터로 6.2L SH-FU-6MSU-1800</t>
+          <t>삼흥에너지 1800℃ 엘레베이터로 6.2L SH-FU-6MSU</t>
         </is>
       </c>
     </row>
@@ -23399,12 +23399,12 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>SH-FU-120RTG300-1Z</t>
+          <t>SH-CVD-PK-50TG300</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>삼흥에너지 1200℃ 회전튜브전기로 1존 300mm 튜브 120Φ SH-FU-120RTG300-1Z</t>
+          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 300mm Ø50 SH-CVD-PK-50TG300</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -23413,13 +23413,13 @@
         </is>
       </c>
       <c r="F386" t="n">
-        <v>12587500</v>
+        <v>9738450</v>
       </c>
       <c r="G386" t="n">
-        <v>12852500</v>
+        <v>9943470</v>
       </c>
       <c r="H386" t="n">
-        <v>13250000</v>
+        <v>10251000</v>
       </c>
       <c r="I386" t="inlineStr">
         <is>
@@ -23428,12 +23428,12 @@
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>https://rndsetup.com/brands/sh-scientific/rotary-tube-furnace/</t>
+          <t>https://rndsetup.com/brands/sh-scientific/vacuum-tube-turnkey/</t>
         </is>
       </c>
       <c r="K386" t="inlineStr">
         <is>
-          <t>https://rndsetup.com/img/product/sh/rotary-tube-furnace.jpg</t>
+          <t>https://rndsetup.com/img/product/sh/vacuum-tube-turnkey.jpg</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
@@ -23443,7 +23443,7 @@
       </c>
       <c r="N386" t="inlineStr">
         <is>
-          <t>삼흥에너지 1200℃ 회전튜브전기로 1존 300mm 튜브 120Φ SH-FU-120RTG300-1Z</t>
+          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 300mm Ø50 SH-CVD-PK-50TG300</t>
         </is>
       </c>
     </row>
@@ -23458,12 +23458,12 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>SH-FU-200RTG300-1Z</t>
+          <t>SH-CVD-PK-80TG300</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>삼흥에너지 1200℃ 회전튜브전기로 1존 300mm 튜브 200Φ SH-FU-200RTG300-1Z</t>
+          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 300mm Ø80 SH-CVD-PK-80TG300</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -23472,13 +23472,13 @@
         </is>
       </c>
       <c r="F387" t="n">
-        <v>18762500</v>
+        <v>11081750</v>
       </c>
       <c r="G387" t="n">
-        <v>19157500</v>
+        <v>11315050</v>
       </c>
       <c r="H387" t="n">
-        <v>19750000</v>
+        <v>11665000</v>
       </c>
       <c r="I387" t="inlineStr">
         <is>
@@ -23487,12 +23487,12 @@
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>https://rndsetup.com/brands/sh-scientific/rotary-tube-furnace/</t>
+          <t>https://rndsetup.com/brands/sh-scientific/vacuum-tube-turnkey/</t>
         </is>
       </c>
       <c r="K387" t="inlineStr">
         <is>
-          <t>https://rndsetup.com/img/product/sh/rotary-tube-furnace.jpg</t>
+          <t>https://rndsetup.com/img/product/sh/vacuum-tube-turnkey.jpg</t>
         </is>
       </c>
       <c r="L387" t="inlineStr">
@@ -23502,7 +23502,7 @@
       </c>
       <c r="N387" t="inlineStr">
         <is>
-          <t>삼흥에너지 1200℃ 회전튜브전기로 1존 300mm 튜브 200Φ SH-FU-200RTG300-1Z</t>
+          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 300mm Ø80 SH-CVD-PK-80TG300</t>
         </is>
       </c>
     </row>
@@ -23517,12 +23517,12 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>SH-FU-250RTG300-1Z</t>
+          <t>SH-CVD-PK-100TG300</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>삼흥에너지 1200℃ 회전튜브전기로 1존 300mm 튜브 250Φ SH-FU-250RTG300-1Z</t>
+          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 300mm Ø100 SH-CVD-PK-100TG300</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
@@ -23531,13 +23531,13 @@
         </is>
       </c>
       <c r="F388" t="n">
-        <v>22942500</v>
+        <v>12668250</v>
       </c>
       <c r="G388" t="n">
-        <v>23425500</v>
+        <v>12934950</v>
       </c>
       <c r="H388" t="n">
-        <v>24150000</v>
+        <v>13335000</v>
       </c>
       <c r="I388" t="inlineStr">
         <is>
@@ -23546,12 +23546,12 @@
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>https://rndsetup.com/brands/sh-scientific/rotary-tube-furnace/</t>
+          <t>https://rndsetup.com/brands/sh-scientific/vacuum-tube-turnkey/</t>
         </is>
       </c>
       <c r="K388" t="inlineStr">
         <is>
-          <t>https://rndsetup.com/img/product/sh/rotary-tube-furnace.jpg</t>
+          <t>https://rndsetup.com/img/product/sh/vacuum-tube-turnkey.jpg</t>
         </is>
       </c>
       <c r="L388" t="inlineStr">
@@ -23561,7 +23561,7 @@
       </c>
       <c r="N388" t="inlineStr">
         <is>
-          <t>삼흥에너지 1200℃ 회전튜브전기로 1존 300mm 튜브 250Φ SH-FU-250RTG300-1Z</t>
+          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 300mm Ø100 SH-CVD-PK-100TG300</t>
         </is>
       </c>
     </row>
@@ -23576,12 +23576,12 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>SH-CVD-50TG300-PK</t>
+          <t>SH-CVD-PK-120TG300</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 300mm Ø50 SH-CVD-50TG300-PK</t>
+          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 300mm Ø120 SH-CVD-PK-120TG300</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
@@ -23590,13 +23590,13 @@
         </is>
       </c>
       <c r="F389" t="n">
-        <v>9738450</v>
+        <v>14739250</v>
       </c>
       <c r="G389" t="n">
-        <v>9943470</v>
+        <v>15049550</v>
       </c>
       <c r="H389" t="n">
-        <v>10251000</v>
+        <v>15515000</v>
       </c>
       <c r="I389" t="inlineStr">
         <is>
@@ -23620,7 +23620,7 @@
       </c>
       <c r="N389" t="inlineStr">
         <is>
-          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 300mm Ø50 SH-CVD-50TG300-PK</t>
+          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 300mm Ø120 SH-CVD-PK-120TG300</t>
         </is>
       </c>
     </row>
@@ -23635,12 +23635,12 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>SH-CVD-80TG300-PK</t>
+          <t>SH-CVD-PK-50TG600</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 300mm Ø80 SH-CVD-80TG300-PK</t>
+          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 600mm Ø50 SH-CVD-PK-50TG600</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
@@ -23649,13 +23649,13 @@
         </is>
       </c>
       <c r="F390" t="n">
-        <v>11081750</v>
+        <v>11134000</v>
       </c>
       <c r="G390" t="n">
-        <v>11315050</v>
+        <v>11368400</v>
       </c>
       <c r="H390" t="n">
-        <v>11665000</v>
+        <v>11720000</v>
       </c>
       <c r="I390" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
       </c>
       <c r="N390" t="inlineStr">
         <is>
-          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 300mm Ø80 SH-CVD-80TG300-PK</t>
+          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 600mm Ø50 SH-CVD-PK-50TG600</t>
         </is>
       </c>
     </row>
@@ -23694,12 +23694,12 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>SH-CVD-100TG300-PK</t>
+          <t>SH-CVD-PK-80TG600</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 300mm Ø100 SH-CVD-100TG300-PK</t>
+          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 600mm Ø80 SH-CVD-PK-80TG600</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -23708,13 +23708,13 @@
         </is>
       </c>
       <c r="F391" t="n">
-        <v>12668250</v>
+        <v>12763250</v>
       </c>
       <c r="G391" t="n">
-        <v>12934950</v>
+        <v>13031950</v>
       </c>
       <c r="H391" t="n">
-        <v>13335000</v>
+        <v>13435000</v>
       </c>
       <c r="I391" t="inlineStr">
         <is>
@@ -23738,7 +23738,7 @@
       </c>
       <c r="N391" t="inlineStr">
         <is>
-          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 300mm Ø100 SH-CVD-100TG300-PK</t>
+          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 600mm Ø80 SH-CVD-PK-80TG600</t>
         </is>
       </c>
     </row>
@@ -23753,12 +23753,12 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>SH-CVD-120TG300-PK</t>
+          <t>SH-CVD-PK-100TG600</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 300mm Ø120 SH-CVD-120TG300-PK</t>
+          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 600mm Ø100 SH-CVD-PK-100TG600</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -23767,13 +23767,13 @@
         </is>
       </c>
       <c r="F392" t="n">
-        <v>14739250</v>
+        <v>14558750</v>
       </c>
       <c r="G392" t="n">
-        <v>15049550</v>
+        <v>14865250</v>
       </c>
       <c r="H392" t="n">
-        <v>15515000</v>
+        <v>15325000</v>
       </c>
       <c r="I392" t="inlineStr">
         <is>
@@ -23797,7 +23797,7 @@
       </c>
       <c r="N392" t="inlineStr">
         <is>
-          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 300mm Ø120 SH-CVD-120TG300-PK</t>
+          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 600mm Ø100 SH-CVD-PK-100TG600</t>
         </is>
       </c>
     </row>
@@ -23812,12 +23812,12 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>SH-CVD-50TG600-PK</t>
+          <t>SH-CVD-PK-120TG600</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 600mm Ø50 SH-CVD-50TG600-PK</t>
+          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 600mm Ø120 SH-CVD-PK-120TG600</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -23826,13 +23826,13 @@
         </is>
       </c>
       <c r="F393" t="n">
-        <v>11134000</v>
+        <v>16107250</v>
       </c>
       <c r="G393" t="n">
-        <v>11368400</v>
+        <v>16446350</v>
       </c>
       <c r="H393" t="n">
-        <v>11720000</v>
+        <v>16955000</v>
       </c>
       <c r="I393" t="inlineStr">
         <is>
@@ -23856,7 +23856,7 @@
       </c>
       <c r="N393" t="inlineStr">
         <is>
-          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 600mm Ø50 SH-CVD-50TG600-PK</t>
+          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 600mm Ø120 SH-CVD-PK-120TG600</t>
         </is>
       </c>
     </row>
@@ -23871,12 +23871,12 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>SH-CVD-80TG600-PK</t>
+          <t>SH-CVD-PK-50TH300</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 600mm Ø80 SH-CVD-80TG600-PK</t>
+          <t>삼흥에너지 CVD 턴키 튜브로 1500℃ 300mm Ø50 SH-CVD-PK-50TH300</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -23885,13 +23885,13 @@
         </is>
       </c>
       <c r="F394" t="n">
-        <v>12763250</v>
+        <v>15366250</v>
       </c>
       <c r="G394" t="n">
-        <v>13031950</v>
+        <v>15689750</v>
       </c>
       <c r="H394" t="n">
-        <v>13435000</v>
+        <v>16175000</v>
       </c>
       <c r="I394" t="inlineStr">
         <is>
@@ -23915,7 +23915,7 @@
       </c>
       <c r="N394" t="inlineStr">
         <is>
-          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 600mm Ø80 SH-CVD-80TG600-PK</t>
+          <t>삼흥에너지 CVD 턴키 튜브로 1500℃ 300mm Ø50 SH-CVD-PK-50TH300</t>
         </is>
       </c>
     </row>
@@ -23930,12 +23930,12 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>SH-CVD-100TG600-PK</t>
+          <t>SH-CVD-PK-80TH300</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 600mm Ø100 SH-CVD-100TG600-PK</t>
+          <t>삼흥에너지 CVD 턴키 튜브로 1500℃ 300mm Ø80 SH-CVD-PK-80TH300</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -23944,13 +23944,13 @@
         </is>
       </c>
       <c r="F395" t="n">
-        <v>14558750</v>
+        <v>17019250</v>
       </c>
       <c r="G395" t="n">
-        <v>14865250</v>
+        <v>17377550</v>
       </c>
       <c r="H395" t="n">
-        <v>15325000</v>
+        <v>17915000</v>
       </c>
       <c r="I395" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="N395" t="inlineStr">
         <is>
-          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 600mm Ø100 SH-CVD-100TG600-PK</t>
+          <t>삼흥에너지 CVD 턴키 튜브로 1500℃ 300mm Ø80 SH-CVD-PK-80TH300</t>
         </is>
       </c>
     </row>
@@ -23989,12 +23989,12 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>SH-CVD-120TG600-PK</t>
+          <t>SH-CVD-PK-100TH300</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 600mm Ø120 SH-CVD-120TG600-PK</t>
+          <t>삼흥에너지 CVD 턴키 튜브로 1500℃ 300mm Ø100 SH-CVD-PK-100TH300</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -24003,13 +24003,13 @@
         </is>
       </c>
       <c r="F396" t="n">
-        <v>16107250</v>
+        <v>21009250</v>
       </c>
       <c r="G396" t="n">
-        <v>16446350</v>
+        <v>21451550</v>
       </c>
       <c r="H396" t="n">
-        <v>16955000</v>
+        <v>22115000</v>
       </c>
       <c r="I396" t="inlineStr">
         <is>
@@ -24033,7 +24033,7 @@
       </c>
       <c r="N396" t="inlineStr">
         <is>
-          <t>삼흥에너지 CVD 턴키 튜브로 1200℃ 600mm Ø120 SH-CVD-120TG600-PK</t>
+          <t>삼흥에너지 CVD 턴키 튜브로 1500℃ 300mm Ø100 SH-CVD-PK-100TH300</t>
         </is>
       </c>
     </row>
@@ -24048,12 +24048,12 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>SH-CVD-50TH300-PK</t>
+          <t>SH-CVD-PK-120TH300</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>삼흥에너지 CVD 턴키 튜브로 1500℃ 300mm Ø50 SH-CVD-50TH300-PK</t>
+          <t>삼흥에너지 CVD 턴키 튜브로 1500℃ 300mm Ø120 SH-CVD-PK-120TH300</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -24062,13 +24062,13 @@
         </is>
       </c>
       <c r="F397" t="n">
-        <v>15366250</v>
+        <v>23868750</v>
       </c>
       <c r="G397" t="n">
-        <v>15689750</v>
+        <v>24371250</v>
       </c>
       <c r="H397" t="n">
-        <v>16175000</v>
+        <v>25125000</v>
       </c>
       <c r="I397" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
       </c>
       <c r="N397" t="inlineStr">
         <is>
-          <t>삼흥에너지 CVD 턴키 튜브로 1500℃ 300mm Ø50 SH-CVD-50TH300-PK</t>
+          <t>삼흥에너지 CVD 턴키 튜브로 1500℃ 300mm Ø120 SH-CVD-PK-120TH300</t>
         </is>
       </c>
     </row>
@@ -24107,12 +24107,12 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>SH-CVD-80TH300-PK</t>
+          <t>SH-CVD-PK-50TS300/18</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>삼흥에너지 CVD 턴키 튜브로 1500℃ 300mm Ø80 SH-CVD-80TH300-PK</t>
+          <t>삼흥에너지 CVD 턴키 튜브로 1800℃ 300mm Ø50 SH-CVD-PK-50TS300/18</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -24121,13 +24121,13 @@
         </is>
       </c>
       <c r="F398" t="n">
-        <v>17019250</v>
+        <v>26908750</v>
       </c>
       <c r="G398" t="n">
-        <v>17377550</v>
+        <v>27475250</v>
       </c>
       <c r="H398" t="n">
-        <v>17915000</v>
+        <v>28325000</v>
       </c>
       <c r="I398" t="inlineStr">
         <is>
@@ -24151,7 +24151,7 @@
       </c>
       <c r="N398" t="inlineStr">
         <is>
-          <t>삼흥에너지 CVD 턴키 튜브로 1500℃ 300mm Ø80 SH-CVD-80TH300-PK</t>
+          <t>삼흥에너지 CVD 턴키 튜브로 1800℃ 300mm Ø50 SH-CVD-PK-50TS300/18</t>
         </is>
       </c>
     </row>
@@ -24166,12 +24166,12 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>SH-CVD-100TH300-PK</t>
+          <t>SH-CVD-PK-80TS300/18</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>삼흥에너지 CVD 턴키 튜브로 1500℃ 300mm Ø100 SH-CVD-100TH300-PK</t>
+          <t>삼흥에너지 CVD 턴키 튜브로 1800℃ 300mm Ø80 SH-CVD-PK-80TS300/18</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -24180,13 +24180,13 @@
         </is>
       </c>
       <c r="F399" t="n">
-        <v>21009250</v>
+        <v>29682750</v>
       </c>
       <c r="G399" t="n">
-        <v>21451550</v>
+        <v>30307650</v>
       </c>
       <c r="H399" t="n">
-        <v>22115000</v>
+        <v>31245000</v>
       </c>
       <c r="I399" t="inlineStr">
         <is>
@@ -24210,7 +24210,7 @@
       </c>
       <c r="N399" t="inlineStr">
         <is>
-          <t>삼흥에너지 CVD 턴키 튜브로 1500℃ 300mm Ø100 SH-CVD-100TH300-PK</t>
+          <t>삼흥에너지 CVD 턴키 튜브로 1800℃ 300mm Ø80 SH-CVD-PK-80TS300/18</t>
         </is>
       </c>
     </row>
@@ -24225,12 +24225,12 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>SH-CVD-120TH300-PK</t>
+          <t>SH-CVD-PK-100TS300/18</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>삼흥에너지 CVD 턴키 튜브로 1500℃ 300mm Ø120 SH-CVD-120TH300-PK</t>
+          <t>삼흥에너지 CVD 턴키 튜브로 1800℃ 300mm Ø100 SH-CVD-PK-100TS300/18</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
@@ -24239,13 +24239,13 @@
         </is>
       </c>
       <c r="F400" t="n">
-        <v>23868750</v>
+        <v>35658250</v>
       </c>
       <c r="G400" t="n">
-        <v>24371250</v>
+        <v>36408950</v>
       </c>
       <c r="H400" t="n">
-        <v>25125000</v>
+        <v>37535000</v>
       </c>
       <c r="I400" t="inlineStr">
         <is>
@@ -24269,7 +24269,7 @@
       </c>
       <c r="N400" t="inlineStr">
         <is>
-          <t>삼흥에너지 CVD 턴키 튜브로 1500℃ 300mm Ø120 SH-CVD-120TH300-PK</t>
+          <t>삼흥에너지 CVD 턴키 튜브로 1800℃ 300mm Ø100 SH-CVD-PK-100TS300/18</t>
         </is>
       </c>
     </row>
@@ -24284,12 +24284,12 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>SH-CVD-50TS300/18-PK</t>
+          <t>SH-CVD-PK-120TS300/18</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>삼흥에너지 CVD 턴키 튜브로 1800℃ 300mm Ø50 SH-CVD-50TS300/18-PK</t>
+          <t>삼흥에너지 CVD 턴키 튜브로 1800℃ 300mm Ø120 SH-CVD-PK-120TS300/18</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -24298,13 +24298,13 @@
         </is>
       </c>
       <c r="F401" t="n">
-        <v>26908750</v>
+        <v>38964250</v>
       </c>
       <c r="G401" t="n">
-        <v>27475250</v>
+        <v>39784550</v>
       </c>
       <c r="H401" t="n">
-        <v>28325000</v>
+        <v>41015000</v>
       </c>
       <c r="I401" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
       </c>
       <c r="N401" t="inlineStr">
         <is>
-          <t>삼흥에너지 CVD 턴키 튜브로 1800℃ 300mm Ø50 SH-CVD-50TS300/18-PK</t>
+          <t>삼흥에너지 CVD 턴키 튜브로 1800℃ 300mm Ø120 SH-CVD-PK-120TS300/18</t>
         </is>
       </c>
     </row>
@@ -24343,12 +24343,12 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>SH-CVD-80TS300/18-PK</t>
+          <t>SH-FU-2MSU</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>삼흥에너지 CVD 턴키 튜브로 1800℃ 300mm Ø80 SH-CVD-80TS300/18-PK</t>
+          <t>삼흥에너지 1700℃ 엘레베이터로 2.2L SH-FU-2MSU</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
@@ -24357,13 +24357,13 @@
         </is>
       </c>
       <c r="F402" t="n">
-        <v>29682750</v>
+        <v>14250000</v>
       </c>
       <c r="G402" t="n">
-        <v>30307650</v>
+        <v>14550000</v>
       </c>
       <c r="H402" t="n">
-        <v>31245000</v>
+        <v>15000000</v>
       </c>
       <c r="I402" t="inlineStr">
         <is>
@@ -24372,12 +24372,12 @@
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>https://rndsetup.com/brands/sh-scientific/vacuum-tube-turnkey/</t>
+          <t>https://rndsetup.com/brands/sh-scientific/elevator-1700/</t>
         </is>
       </c>
       <c r="K402" t="inlineStr">
         <is>
-          <t>https://rndsetup.com/img/product/sh/vacuum-tube-turnkey.jpg</t>
+          <t>https://rndsetup.com/img/product/sh/elevator-1700.jpg</t>
         </is>
       </c>
       <c r="L402" t="inlineStr">
@@ -24387,7 +24387,7 @@
       </c>
       <c r="N402" t="inlineStr">
         <is>
-          <t>삼흥에너지 CVD 턴키 튜브로 1800℃ 300mm Ø80 SH-CVD-80TS300/18-PK</t>
+          <t>삼흥에너지 1700℃ 엘레베이터로 2.2L SH-FU-2MSU</t>
         </is>
       </c>
     </row>
@@ -24402,12 +24402,12 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>SH-CVD-100TS300/18-PK</t>
+          <t>SH-FU-4MSU</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>삼흥에너지 CVD 턴키 튜브로 1800℃ 300mm Ø100 SH-CVD-100TS300/18-PK</t>
+          <t>삼흥에너지 1700℃ 엘레베이터로 3.8L SH-FU-4MSU</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
@@ -24416,13 +24416,13 @@
         </is>
       </c>
       <c r="F403" t="n">
-        <v>35658250</v>
+        <v>15722500</v>
       </c>
       <c r="G403" t="n">
-        <v>36408950</v>
+        <v>16053500</v>
       </c>
       <c r="H403" t="n">
-        <v>37535000</v>
+        <v>16550000</v>
       </c>
       <c r="I403" t="inlineStr">
         <is>
@@ -24431,12 +24431,12 @@
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>https://rndsetup.com/brands/sh-scientific/vacuum-tube-turnkey/</t>
+          <t>https://rndsetup.com/brands/sh-scientific/elevator-1700/</t>
         </is>
       </c>
       <c r="K403" t="inlineStr">
         <is>
-          <t>https://rndsetup.com/img/product/sh/vacuum-tube-turnkey.jpg</t>
+          <t>https://rndsetup.com/img/product/sh/elevator-1700.jpg</t>
         </is>
       </c>
       <c r="L403" t="inlineStr">
@@ -24446,7 +24446,7 @@
       </c>
       <c r="N403" t="inlineStr">
         <is>
-          <t>삼흥에너지 CVD 턴키 튜브로 1800℃ 300mm Ø100 SH-CVD-100TS300/18-PK</t>
+          <t>삼흥에너지 1700℃ 엘레베이터로 3.8L SH-FU-4MSU</t>
         </is>
       </c>
     </row>
@@ -24461,12 +24461,12 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>SH-CVD-120TS300/18-PK</t>
+          <t>SH-FU-6MSU</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>삼흥에너지 CVD 턴키 튜브로 1800℃ 300mm Ø120 SH-CVD-120TS300/18-PK</t>
+          <t>삼흥에너지 1700℃ 엘레베이터로 6.2L SH-FU-6MSU</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
@@ -24475,13 +24475,13 @@
         </is>
       </c>
       <c r="F404" t="n">
-        <v>38964250</v>
+        <v>17480000</v>
       </c>
       <c r="G404" t="n">
-        <v>39784550</v>
+        <v>17848000</v>
       </c>
       <c r="H404" t="n">
-        <v>41015000</v>
+        <v>18400000</v>
       </c>
       <c r="I404" t="inlineStr">
         <is>
@@ -24490,12 +24490,12 @@
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>https://rndsetup.com/brands/sh-scientific/vacuum-tube-turnkey/</t>
+          <t>https://rndsetup.com/brands/sh-scientific/elevator-1700/</t>
         </is>
       </c>
       <c r="K404" t="inlineStr">
         <is>
-          <t>https://rndsetup.com/img/product/sh/vacuum-tube-turnkey.jpg</t>
+          <t>https://rndsetup.com/img/product/sh/elevator-1700.jpg</t>
         </is>
       </c>
       <c r="L404" t="inlineStr">
@@ -24505,7 +24505,7 @@
       </c>
       <c r="N404" t="inlineStr">
         <is>
-          <t>삼흥에너지 CVD 턴키 튜브로 1800℃ 300mm Ø120 SH-CVD-120TS300/18-PK</t>
+          <t>삼흥에너지 1700℃ 엘레베이터로 6.2L SH-FU-6MSU</t>
         </is>
       </c>
     </row>
@@ -24520,12 +24520,12 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>SH-FU-2MSU-1700</t>
+          <t>SH-FU-100RKH600</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>삼흥에너지 1700℃ 엘레베이터로 2.2L SH-FU-2MSU-1700</t>
+          <t>삼흥에너지 1500℃ 연속식 회전튜브전기로 2존 Φ100 SH-FU-100RKH600</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -24534,13 +24534,13 @@
         </is>
       </c>
       <c r="F405" t="n">
-        <v>14250000</v>
+        <v>47500000</v>
       </c>
       <c r="G405" t="n">
-        <v>14550000</v>
+        <v>48500000</v>
       </c>
       <c r="H405" t="n">
-        <v>15000000</v>
+        <v>50000000</v>
       </c>
       <c r="I405" t="inlineStr">
         <is>
@@ -24549,12 +24549,12 @@
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>https://rndsetup.com/brands/sh-scientific/elevator-1700/</t>
+          <t>https://rndsetup.com/brands/sh-scientific/rotary-kiln-1500-2zone/</t>
         </is>
       </c>
       <c r="K405" t="inlineStr">
         <is>
-          <t>https://rndsetup.com/img/product/sh/elevator-1700.jpg</t>
+          <t>https://rndsetup.com/img/product/sh/rotary-kiln-1500-2zone.jpg</t>
         </is>
       </c>
       <c r="L405" t="inlineStr">
@@ -24564,7 +24564,7 @@
       </c>
       <c r="N405" t="inlineStr">
         <is>
-          <t>삼흥에너지 1700℃ 엘레베이터로 2.2L SH-FU-2MSU-1700</t>
+          <t>삼흥에너지 1500℃ 연속식 회전튜브전기로 2존 Φ100 SH-FU-100RKH600</t>
         </is>
       </c>
     </row>
@@ -24579,12 +24579,12 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>SH-FU-4MSU-1700</t>
+          <t>SH-FU-120RKH600</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>삼흥에너지 1700℃ 엘레베이터로 3.8L SH-FU-4MSU-1700</t>
+          <t>삼흥에너지 1500℃ 연속식 회전튜브전기로 2존 Φ120 SH-FU-120RKH600</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -24593,13 +24593,13 @@
         </is>
       </c>
       <c r="F406" t="n">
-        <v>15722500</v>
+        <v>55005000</v>
       </c>
       <c r="G406" t="n">
-        <v>16053500</v>
+        <v>56163000</v>
       </c>
       <c r="H406" t="n">
-        <v>16550000</v>
+        <v>57900000</v>
       </c>
       <c r="I406" t="inlineStr">
         <is>
@@ -24608,12 +24608,12 @@
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>https://rndsetup.com/brands/sh-scientific/elevator-1700/</t>
+          <t>https://rndsetup.com/brands/sh-scientific/rotary-kiln-1500-2zone/</t>
         </is>
       </c>
       <c r="K406" t="inlineStr">
         <is>
-          <t>https://rndsetup.com/img/product/sh/elevator-1700.jpg</t>
+          <t>https://rndsetup.com/img/product/sh/rotary-kiln-1500-2zone.jpg</t>
         </is>
       </c>
       <c r="L406" t="inlineStr">
@@ -24623,7 +24623,7 @@
       </c>
       <c r="N406" t="inlineStr">
         <is>
-          <t>삼흥에너지 1700℃ 엘레베이터로 3.8L SH-FU-4MSU-1700</t>
+          <t>삼흥에너지 1500℃ 연속식 회전튜브전기로 2존 Φ120 SH-FU-120RKH600</t>
         </is>
       </c>
     </row>
@@ -24638,12 +24638,12 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>SH-FU-6MSU-1700</t>
+          <t>SH-FU-100RKH900</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>삼흥에너지 1700℃ 엘레베이터로 6.2L SH-FU-6MSU-1700</t>
+          <t>삼흥에너지 1500℃ 연속식 회전튜브전기로 3존 Φ100 SH-FU-100RKH900</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
@@ -24652,13 +24652,13 @@
         </is>
       </c>
       <c r="F407" t="n">
-        <v>17480000</v>
+        <v>57950000</v>
       </c>
       <c r="G407" t="n">
-        <v>17848000</v>
+        <v>59170000</v>
       </c>
       <c r="H407" t="n">
-        <v>18400000</v>
+        <v>61000000</v>
       </c>
       <c r="I407" t="inlineStr">
         <is>
@@ -24667,12 +24667,12 @@
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>https://rndsetup.com/brands/sh-scientific/elevator-1700/</t>
+          <t>https://rndsetup.com/brands/sh-scientific/rotary-kiln-1500-3zone/</t>
         </is>
       </c>
       <c r="K407" t="inlineStr">
         <is>
-          <t>https://rndsetup.com/img/product/sh/elevator-1700.jpg</t>
+          <t>https://rndsetup.com/img/product/sh/rotary-kiln-1500-3zone.jpg</t>
         </is>
       </c>
       <c r="L407" t="inlineStr">
@@ -24682,7 +24682,7 @@
       </c>
       <c r="N407" t="inlineStr">
         <is>
-          <t>삼흥에너지 1700℃ 엘레베이터로 6.2L SH-FU-6MSU-1700</t>
+          <t>삼흥에너지 1500℃ 연속식 회전튜브전기로 3존 Φ100 SH-FU-100RKH900</t>
         </is>
       </c>
     </row>
@@ -24697,12 +24697,12 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>SH-FU-100RKH600</t>
+          <t>SH-FU-120RKH900</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>삼흥에너지 1500℃ 연속식 회전튜브전기로 2존 Φ100 SH-FU-100RKH600</t>
+          <t>삼흥에너지 1500℃ 연속식 회전튜브전기로 3존 Φ120 SH-FU-120RKH900</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -24711,13 +24711,13 @@
         </is>
       </c>
       <c r="F408" t="n">
-        <v>47500000</v>
+        <v>67450000</v>
       </c>
       <c r="G408" t="n">
-        <v>48500000</v>
+        <v>68870000</v>
       </c>
       <c r="H408" t="n">
-        <v>50000000</v>
+        <v>71000000</v>
       </c>
       <c r="I408" t="inlineStr">
         <is>
@@ -24726,12 +24726,12 @@
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>https://rndsetup.com/brands/sh-scientific/rotary-kiln-1500-2zone/</t>
+          <t>https://rndsetup.com/brands/sh-scientific/rotary-kiln-1500-3zone/</t>
         </is>
       </c>
       <c r="K408" t="inlineStr">
         <is>
-          <t>https://rndsetup.com/img/product/sh/rotary-kiln-1500-2zone.jpg</t>
+          <t>https://rndsetup.com/img/product/sh/rotary-kiln-1500-3zone.jpg</t>
         </is>
       </c>
       <c r="L408" t="inlineStr">
@@ -24741,7 +24741,7 @@
       </c>
       <c r="N408" t="inlineStr">
         <is>
-          <t>삼흥에너지 1500℃ 연속식 회전튜브전기로 2존 Φ100 SH-FU-100RKH600</t>
+          <t>삼흥에너지 1500℃ 연속식 회전튜브전기로 3존 Φ120 SH-FU-120RKH900</t>
         </is>
       </c>
     </row>
@@ -24756,12 +24756,12 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>SH-FU-120RKH600</t>
+          <t>SH-FU-5MGQ</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>삼흥에너지 1500℃ 연속식 회전튜브전기로 2존 Φ120 SH-FU-120RKH600</t>
+          <t>삼흥에너지 1200℃ 석영챔버 머플로 4.5L SH-FU-5MGQ</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
@@ -24770,13 +24770,13 @@
         </is>
       </c>
       <c r="F409" t="n">
-        <v>55005000</v>
+        <v>3325000</v>
       </c>
       <c r="G409" t="n">
-        <v>56163000</v>
+        <v>3395000</v>
       </c>
       <c r="H409" t="n">
-        <v>57900000</v>
+        <v>3500000</v>
       </c>
       <c r="I409" t="inlineStr">
         <is>
@@ -24785,12 +24785,12 @@
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>https://rndsetup.com/brands/sh-scientific/rotary-kiln-1500-2zone/</t>
+          <t>https://rndsetup.com/brands/sh-scientific/muffle-1200-quartz/</t>
         </is>
       </c>
       <c r="K409" t="inlineStr">
         <is>
-          <t>https://rndsetup.com/img/product/sh/rotary-kiln-1500-2zone.jpg</t>
+          <t>https://rndsetup.com/img/product/sh/muffle-1200-quartz.jpg</t>
         </is>
       </c>
       <c r="L409" t="inlineStr">
@@ -24800,7 +24800,7 @@
       </c>
       <c r="N409" t="inlineStr">
         <is>
-          <t>삼흥에너지 1500℃ 연속식 회전튜브전기로 2존 Φ120 SH-FU-120RKH600</t>
+          <t>삼흥에너지 1200℃ 석영챔버 머플로 4.5L SH-FU-5MGQ</t>
         </is>
       </c>
     </row>
@@ -24815,12 +24815,12 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>SH-FU-100RKH900</t>
+          <t>SH-FU-14MGQ</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>삼흥에너지 1500℃ 연속식 회전튜브전기로 3존 Φ100 SH-FU-100RKH900</t>
+          <t>삼흥에너지 1200℃ 석영챔버 머플로 14L SH-FU-14MGQ</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
@@ -24829,13 +24829,13 @@
         </is>
       </c>
       <c r="F410" t="n">
-        <v>57950000</v>
+        <v>4750000</v>
       </c>
       <c r="G410" t="n">
-        <v>59170000</v>
+        <v>4850000</v>
       </c>
       <c r="H410" t="n">
-        <v>61000000</v>
+        <v>5000000</v>
       </c>
       <c r="I410" t="inlineStr">
         <is>
@@ -24844,12 +24844,12 @@
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>https://rndsetup.com/brands/sh-scientific/rotary-kiln-1500-3zone/</t>
+          <t>https://rndsetup.com/brands/sh-scientific/muffle-1200-quartz/</t>
         </is>
       </c>
       <c r="K410" t="inlineStr">
         <is>
-          <t>https://rndsetup.com/img/product/sh/rotary-kiln-1500-3zone.jpg</t>
+          <t>https://rndsetup.com/img/product/sh/muffle-1200-quartz.jpg</t>
         </is>
       </c>
       <c r="L410" t="inlineStr">
@@ -24859,7 +24859,7 @@
       </c>
       <c r="N410" t="inlineStr">
         <is>
-          <t>삼흥에너지 1500℃ 연속식 회전튜브전기로 3존 Φ100 SH-FU-100RKH900</t>
+          <t>삼흥에너지 1200℃ 석영챔버 머플로 14L SH-FU-14MGQ</t>
         </is>
       </c>
     </row>
@@ -24874,12 +24874,12 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>SH-FU-120RKH900</t>
+          <t>SH-FU-27MGQ</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>삼흥에너지 1500℃ 연속식 회전튜브전기로 3존 Φ120 SH-FU-120RKH900</t>
+          <t>삼흥에너지 1200℃ 석영챔버 머플로 27L SH-FU-27MGQ</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -24888,13 +24888,13 @@
         </is>
       </c>
       <c r="F411" t="n">
-        <v>67450000</v>
+        <v>7600000</v>
       </c>
       <c r="G411" t="n">
-        <v>68870000</v>
+        <v>7760000</v>
       </c>
       <c r="H411" t="n">
-        <v>71000000</v>
+        <v>8000000</v>
       </c>
       <c r="I411" t="inlineStr">
         <is>
@@ -24903,12 +24903,12 @@
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>https://rndsetup.com/brands/sh-scientific/rotary-kiln-1500-3zone/</t>
+          <t>https://rndsetup.com/brands/sh-scientific/muffle-1200-quartz/</t>
         </is>
       </c>
       <c r="K411" t="inlineStr">
         <is>
-          <t>https://rndsetup.com/img/product/sh/rotary-kiln-1500-3zone.jpg</t>
+          <t>https://rndsetup.com/img/product/sh/muffle-1200-quartz.jpg</t>
         </is>
       </c>
       <c r="L411" t="inlineStr">
@@ -24918,7 +24918,7 @@
       </c>
       <c r="N411" t="inlineStr">
         <is>
-          <t>삼흥에너지 1500℃ 연속식 회전튜브전기로 3존 Φ120 SH-FU-120RKH900</t>
+          <t>삼흥에너지 1200℃ 석영챔버 머플로 27L SH-FU-27MGQ</t>
         </is>
       </c>
     </row>
@@ -24933,12 +24933,12 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>SH-FU-5MGQ</t>
+          <t>SH-FU-64MGV</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>삼흥에너지 1200℃ 석영챔버 머플로 4.5L SH-FU-5MGQ</t>
+          <t>삼흥에너지 1200℃ 진공 머플로 64L SH-FU-64MGV</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -24947,13 +24947,13 @@
         </is>
       </c>
       <c r="F412" t="n">
-        <v>3325000</v>
+        <v>29877500</v>
       </c>
       <c r="G412" t="n">
-        <v>3395000</v>
+        <v>30506500</v>
       </c>
       <c r="H412" t="n">
-        <v>3500000</v>
+        <v>31450000</v>
       </c>
       <c r="I412" t="inlineStr">
         <is>
@@ -24962,12 +24962,12 @@
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>https://rndsetup.com/brands/sh-scientific/muffle-1200-quartz/</t>
+          <t>https://rndsetup.com/brands/sh-scientific/vacuum-muffle-1200/</t>
         </is>
       </c>
       <c r="K412" t="inlineStr">
         <is>
-          <t>https://rndsetup.com/img/product/sh/muffle-1200-quartz.jpg</t>
+          <t>https://rndsetup.com/img/product/sh/vacuum-muffle-1200.jpg</t>
         </is>
       </c>
       <c r="L412" t="inlineStr">
@@ -24977,7 +24977,7 @@
       </c>
       <c r="N412" t="inlineStr">
         <is>
-          <t>삼흥에너지 1200℃ 석영챔버 머플로 4.5L SH-FU-5MGQ</t>
+          <t>삼흥에너지 1200℃ 진공 머플로 64L SH-FU-64MGV</t>
         </is>
       </c>
     </row>
@@ -24992,12 +24992,12 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>SH-FU-14MGQ</t>
+          <t>SH-FU-125MGV</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>삼흥에너지 1200℃ 석영챔버 머플로 14L SH-FU-14MGQ</t>
+          <t>삼흥에너지 1200℃ 진공 머플로 125L SH-FU-125MGV</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -25006,13 +25006,13 @@
         </is>
       </c>
       <c r="F413" t="n">
-        <v>4750000</v>
+        <v>39653000</v>
       </c>
       <c r="G413" t="n">
-        <v>4850000</v>
+        <v>40487800</v>
       </c>
       <c r="H413" t="n">
-        <v>5000000</v>
+        <v>41740000</v>
       </c>
       <c r="I413" t="inlineStr">
         <is>
@@ -25021,12 +25021,12 @@
       </c>
       <c r="J413" t="inlineStr">
         <is>
-          <t>https://rndsetup.com/brands/sh-scientific/muffle-1200-quartz/</t>
+          <t>https://rndsetup.com/brands/sh-scientific/vacuum-muffle-1200/</t>
         </is>
       </c>
       <c r="K413" t="inlineStr">
         <is>
-          <t>https://rndsetup.com/img/product/sh/muffle-1200-quartz.jpg</t>
+          <t>https://rndsetup.com/img/product/sh/vacuum-muffle-1200.jpg</t>
         </is>
       </c>
       <c r="L413" t="inlineStr">
@@ -25036,7 +25036,7 @@
       </c>
       <c r="N413" t="inlineStr">
         <is>
-          <t>삼흥에너지 1200℃ 석영챔버 머플로 14L SH-FU-14MGQ</t>
+          <t>삼흥에너지 1200℃ 진공 머플로 125L SH-FU-125MGV</t>
         </is>
       </c>
     </row>
@@ -25051,12 +25051,12 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>SH-FU-27MGQ</t>
+          <t>SH-LABSTEAM5</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>삼흥에너지 1200℃ 석영챔버 머플로 27L SH-FU-27MGQ</t>
+          <t>삼흥에너지 Benchtop 스팀 제너레이터 5L SH-LABSTEAM5</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -25065,13 +25065,13 @@
         </is>
       </c>
       <c r="F414" t="n">
-        <v>7600000</v>
+        <v>2109000</v>
       </c>
       <c r="G414" t="n">
-        <v>7760000</v>
+        <v>2153400</v>
       </c>
       <c r="H414" t="n">
-        <v>8000000</v>
+        <v>2220000</v>
       </c>
       <c r="I414" t="inlineStr">
         <is>
@@ -25080,12 +25080,12 @@
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>https://rndsetup.com/brands/sh-scientific/muffle-1200-quartz/</t>
+          <t>https://rndsetup.com/brands/sh-scientific/steam-generator/</t>
         </is>
       </c>
       <c r="K414" t="inlineStr">
         <is>
-          <t>https://rndsetup.com/img/product/sh/muffle-1200-quartz.jpg</t>
+          <t>https://silhumsil.com/web/product/medium/202603/4ca8ad62a9a5eddcd3d4ed3ccc876cf8.jpg</t>
         </is>
       </c>
       <c r="L414" t="inlineStr">
@@ -25094,183 +25094,6 @@
         </is>
       </c>
       <c r="N414" t="inlineStr">
-        <is>
-          <t>삼흥에너지 1200℃ 석영챔버 머플로 27L SH-FU-27MGQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="415">
-      <c r="A415" t="n">
-        <v>412</v>
-      </c>
-      <c r="B415" t="inlineStr">
-        <is>
-          <t>SH Scientific</t>
-        </is>
-      </c>
-      <c r="C415" t="inlineStr">
-        <is>
-          <t>SH-FU-64MGV</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr">
-        <is>
-          <t>삼흥에너지 1200℃ 진공 머플로 64L SH-FU-64MGV</t>
-        </is>
-      </c>
-      <c r="E415" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="F415" t="n">
-        <v>29877500</v>
-      </c>
-      <c r="G415" t="n">
-        <v>30506500</v>
-      </c>
-      <c r="H415" t="n">
-        <v>31450000</v>
-      </c>
-      <c r="I415" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J415" t="inlineStr">
-        <is>
-          <t>https://rndsetup.com/brands/sh-scientific/vacuum-muffle-1200/</t>
-        </is>
-      </c>
-      <c r="K415" t="inlineStr">
-        <is>
-          <t>https://rndsetup.com/img/product/sh/vacuum-muffle-1200.jpg</t>
-        </is>
-      </c>
-      <c r="L415" t="inlineStr">
-        <is>
-          <t>재고 문의</t>
-        </is>
-      </c>
-      <c r="N415" t="inlineStr">
-        <is>
-          <t>삼흥에너지 1200℃ 진공 머플로 64L SH-FU-64MGV</t>
-        </is>
-      </c>
-    </row>
-    <row r="416">
-      <c r="A416" t="n">
-        <v>413</v>
-      </c>
-      <c r="B416" t="inlineStr">
-        <is>
-          <t>SH Scientific</t>
-        </is>
-      </c>
-      <c r="C416" t="inlineStr">
-        <is>
-          <t>SH-FU-125MGV</t>
-        </is>
-      </c>
-      <c r="D416" t="inlineStr">
-        <is>
-          <t>삼흥에너지 1200℃ 진공 머플로 125L SH-FU-125MGV</t>
-        </is>
-      </c>
-      <c r="E416" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="F416" t="n">
-        <v>39653000</v>
-      </c>
-      <c r="G416" t="n">
-        <v>40487800</v>
-      </c>
-      <c r="H416" t="n">
-        <v>41740000</v>
-      </c>
-      <c r="I416" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J416" t="inlineStr">
-        <is>
-          <t>https://rndsetup.com/brands/sh-scientific/vacuum-muffle-1200/</t>
-        </is>
-      </c>
-      <c r="K416" t="inlineStr">
-        <is>
-          <t>https://rndsetup.com/img/product/sh/vacuum-muffle-1200.jpg</t>
-        </is>
-      </c>
-      <c r="L416" t="inlineStr">
-        <is>
-          <t>재고 문의</t>
-        </is>
-      </c>
-      <c r="N416" t="inlineStr">
-        <is>
-          <t>삼흥에너지 1200℃ 진공 머플로 125L SH-FU-125MGV</t>
-        </is>
-      </c>
-    </row>
-    <row r="417">
-      <c r="A417" t="n">
-        <v>414</v>
-      </c>
-      <c r="B417" t="inlineStr">
-        <is>
-          <t>SH Scientific</t>
-        </is>
-      </c>
-      <c r="C417" t="inlineStr">
-        <is>
-          <t>SH-LABSTEAM5</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>삼흥에너지 Benchtop 스팀 제너레이터 5L SH-LABSTEAM5</t>
-        </is>
-      </c>
-      <c r="E417" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="F417" t="n">
-        <v>2109000</v>
-      </c>
-      <c r="G417" t="n">
-        <v>2153400</v>
-      </c>
-      <c r="H417" t="n">
-        <v>2220000</v>
-      </c>
-      <c r="I417" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J417" t="inlineStr">
-        <is>
-          <t>https://rndsetup.com/brands/sh-scientific/steam-generator/</t>
-        </is>
-      </c>
-      <c r="K417" t="inlineStr">
-        <is>
-          <t>https://silhumsil.com/web/product/medium/202603/4ca8ad62a9a5eddcd3d4ed3ccc876cf8.jpg</t>
-        </is>
-      </c>
-      <c r="L417" t="inlineStr">
-        <is>
-          <t>재고 문의</t>
-        </is>
-      </c>
-      <c r="N417" t="inlineStr">
         <is>
           <t>삼흥에너지 Benchtop 스팀 제너레이터 5L SH-LABSTEAM5</t>
         </is>
